--- a/sales_by_year.xlsx
+++ b/sales_by_year.xlsx
@@ -444,79 +444,71 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2022</v>
       </c>
       <c r="B2" t="n">
-        <v>1607</v>
+        <v>1692</v>
       </c>
       <c r="C2" t="n">
-        <v>12641672.21289983</v>
+        <v>16316694.169</v>
       </c>
       <c r="D2" t="n">
-        <v>7866.62863279392</v>
+        <v>9643.436270094562</v>
       </c>
       <c r="E2" t="n">
-        <v>1406</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2023</v>
       </c>
       <c r="B3" t="n">
-        <v>3915</v>
+        <v>3830</v>
       </c>
       <c r="C3" t="n">
-        <v>33524301.32599971</v>
+        <v>35514705.668</v>
       </c>
       <c r="D3" t="n">
-        <v>8563.039930012699</v>
+        <v>9272.769103916449</v>
       </c>
       <c r="E3" t="n">
-        <v>3162</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2024</v>
       </c>
       <c r="B4" t="n">
-        <v>14182</v>
+        <v>14244</v>
       </c>
       <c r="C4" t="n">
-        <v>43622479.05369764</v>
+        <v>49020486.512</v>
       </c>
       <c r="D4" t="n">
-        <v>3075.90460116328</v>
+        <v>3441.483186745296</v>
       </c>
       <c r="E4" t="n">
-        <v>11095</v>
+        <v>11145</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2025</v>
       </c>
       <c r="B5" t="n">
-        <v>11761</v>
+        <v>11699</v>
       </c>
       <c r="C5" t="n">
-        <v>20057928.81130027</v>
+        <v>22364899.7669</v>
       </c>
       <c r="D5" t="n">
-        <v>1705.46116922883</v>
+        <v>1911.693287195487</v>
       </c>
       <c r="E5" t="n">
-        <v>10354</v>
+        <v>10303</v>
       </c>
     </row>
   </sheetData>
